--- a/Convert_from_xlsx_to_Json/table_normalization/economy-table99.xlsx
+++ b/Convert_from_xlsx_to_Json/table_normalization/economy-table99.xlsx
@@ -132,7 +132,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -142,12 +142,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -194,7 +188,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -202,26 +196,27 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="3" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -529,7 +524,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -546,78 +541,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="27.5">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="13" thickBot="1"/>
     <row r="5" spans="1:10" ht="29.25" customHeight="1" thickTop="1" thickBot="1">
       <c r="A5" s="2"/>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="H5" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="I5" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="12" t="s">
+      <c r="J5" s="21" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="13">
-      <c r="A6" s="15"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="19"/>
-      <c r="I6" s="19"/>
-      <c r="J6" s="19"/>
+      <c r="A6" s="11"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="19"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
-      <c r="I7" s="19"/>
-      <c r="J7" s="19"/>
+      <c r="A7" s="15"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="15"/>
+      <c r="I7" s="15"/>
+      <c r="J7" s="15"/>
     </row>
     <row r="8" spans="1:10" ht="13">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="19"/>
-      <c r="J8" s="19"/>
+      <c r="B8" s="15"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="15"/>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="4" t="s">
@@ -716,560 +711,560 @@
       </c>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12" s="15">
         <v>68</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12" s="15">
         <v>36</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D12" s="15">
         <v>3</v>
       </c>
-      <c r="E12" s="1">
-        <v>0</v>
-      </c>
-      <c r="F12" s="1">
-        <v>0</v>
-      </c>
-      <c r="G12" s="1">
+      <c r="E12" s="15">
+        <v>0</v>
+      </c>
+      <c r="F12" s="15">
+        <v>0</v>
+      </c>
+      <c r="G12" s="15">
         <v>4</v>
       </c>
-      <c r="H12" s="1">
-        <v>0</v>
-      </c>
-      <c r="I12" s="1">
+      <c r="H12" s="15">
+        <v>0</v>
+      </c>
+      <c r="I12" s="15">
         <v>5</v>
       </c>
-      <c r="J12" s="1">
+      <c r="J12" s="15">
         <v>116</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="13">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="18">
         <v>60832</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="18">
         <v>5550</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="18">
         <v>492</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="18">
         <v>182</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="18">
         <v>41</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G13" s="18">
         <v>6627</v>
       </c>
-      <c r="H13" s="3">
+      <c r="H13" s="18">
         <v>754</v>
       </c>
-      <c r="I13" s="3">
+      <c r="I13" s="18">
         <v>1167</v>
       </c>
-      <c r="J13" s="3">
+      <c r="J13" s="18">
         <v>75645</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="13">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="14"/>
-      <c r="J14" s="14"/>
+      <c r="A14" s="17"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="18"/>
+      <c r="J14" s="18"/>
     </row>
     <row r="15" spans="1:10" ht="13">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="14"/>
-      <c r="J15" s="14"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="18"/>
+      <c r="J15" s="18"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B16" s="19">
         <v>9233</v>
       </c>
-      <c r="C16" s="4">
+      <c r="C16" s="19">
         <v>2379</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="19">
         <v>166</v>
       </c>
-      <c r="E16" s="4">
+      <c r="E16" s="19">
         <v>117</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F16" s="19">
         <v>14</v>
       </c>
-      <c r="G16" s="4">
+      <c r="G16" s="19">
         <v>168</v>
       </c>
-      <c r="H16" s="4">
+      <c r="H16" s="19">
         <v>183</v>
       </c>
-      <c r="I16" s="4">
+      <c r="I16" s="19">
         <v>465</v>
       </c>
-      <c r="J16" s="1">
+      <c r="J16" s="15">
         <v>12725</v>
       </c>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="B17" s="4">
+      <c r="B17" s="19">
         <v>2226</v>
       </c>
-      <c r="C17" s="4">
+      <c r="C17" s="19">
         <v>150</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17" s="19">
         <v>22</v>
       </c>
-      <c r="E17" s="4">
+      <c r="E17" s="19">
         <v>8</v>
       </c>
-      <c r="F17" s="4">
+      <c r="F17" s="19">
         <v>12</v>
       </c>
-      <c r="G17" s="4">
+      <c r="G17" s="19">
         <v>33</v>
       </c>
-      <c r="H17" s="4">
+      <c r="H17" s="19">
         <v>64</v>
       </c>
-      <c r="I17" s="4">
+      <c r="I17" s="19">
         <v>34</v>
       </c>
-      <c r="J17" s="4">
+      <c r="J17" s="19">
         <v>2549</v>
       </c>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="B18" s="4">
+      <c r="B18" s="19">
         <v>98</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="4">
-        <v>0</v>
-      </c>
-      <c r="E18" s="4">
-        <v>0</v>
-      </c>
-      <c r="F18" s="4">
-        <v>0</v>
-      </c>
-      <c r="G18" s="7" t="s">
+      <c r="D18" s="19">
+        <v>0</v>
+      </c>
+      <c r="E18" s="19">
+        <v>0</v>
+      </c>
+      <c r="F18" s="19">
+        <v>0</v>
+      </c>
+      <c r="G18" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H18" s="4">
+      <c r="H18" s="19">
         <v>11</v>
       </c>
-      <c r="I18" s="7" t="s">
+      <c r="I18" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="J18" s="4">
+      <c r="J18" s="19">
         <v>161</v>
       </c>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B19" s="4">
-        <v>0</v>
-      </c>
-      <c r="C19" s="7" t="s">
+      <c r="B19" s="19">
+        <v>0</v>
+      </c>
+      <c r="C19" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="4">
-        <v>0</v>
-      </c>
-      <c r="E19" s="4">
-        <v>0</v>
-      </c>
-      <c r="F19" s="4">
-        <v>0</v>
-      </c>
-      <c r="G19" s="7" t="s">
+      <c r="D19" s="19">
+        <v>0</v>
+      </c>
+      <c r="E19" s="19">
+        <v>0</v>
+      </c>
+      <c r="F19" s="19">
+        <v>0</v>
+      </c>
+      <c r="G19" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H19" s="4">
-        <v>0</v>
-      </c>
-      <c r="I19" s="7" t="s">
+      <c r="H19" s="19">
+        <v>0</v>
+      </c>
+      <c r="I19" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="J19" s="4">
+      <c r="J19" s="19">
         <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="13">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B20" s="18">
         <v>11557</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="18">
         <v>2561</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="18">
         <v>188</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="18">
         <v>125</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="18">
         <v>26</v>
       </c>
-      <c r="G20" s="3">
+      <c r="G20" s="18">
         <v>224</v>
       </c>
-      <c r="H20" s="3">
+      <c r="H20" s="18">
         <v>258</v>
       </c>
-      <c r="I20" s="3">
+      <c r="I20" s="18">
         <v>501</v>
       </c>
-      <c r="J20" s="3">
+      <c r="J20" s="18">
         <v>15440</v>
       </c>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="20"/>
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="19"/>
-      <c r="I21" s="19"/>
-      <c r="J21" s="19"/>
+      <c r="A21" s="16"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="15"/>
+      <c r="I21" s="15"/>
+      <c r="J21" s="15"/>
     </row>
     <row r="22" spans="1:10" ht="13">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="19"/>
-      <c r="I22" s="19"/>
-      <c r="J22" s="19"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="15"/>
+      <c r="I22" s="15"/>
+      <c r="J22" s="15"/>
     </row>
     <row r="23" spans="1:10">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B23" s="1">
+      <c r="B23" s="15">
         <v>406910</v>
       </c>
-      <c r="C23" s="1">
+      <c r="C23" s="15">
         <v>25713</v>
       </c>
-      <c r="D23" s="1">
+      <c r="D23" s="15">
         <v>2879</v>
       </c>
-      <c r="E23" s="1">
+      <c r="E23" s="15">
         <v>188</v>
       </c>
-      <c r="F23" s="1">
+      <c r="F23" s="15">
         <v>66</v>
       </c>
-      <c r="G23" s="1">
+      <c r="G23" s="15">
         <v>1129</v>
       </c>
-      <c r="H23" s="1">
+      <c r="H23" s="15">
         <v>498</v>
       </c>
-      <c r="I23" s="1">
+      <c r="I23" s="15">
         <v>3893</v>
       </c>
-      <c r="J23" s="1">
+      <c r="J23" s="15">
         <v>441276</v>
       </c>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="B24" s="1">
+      <c r="B24" s="15">
         <v>23531</v>
       </c>
-      <c r="C24" s="1">
+      <c r="C24" s="15">
         <v>1749</v>
       </c>
-      <c r="D24" s="1">
+      <c r="D24" s="15">
         <v>161</v>
       </c>
-      <c r="E24" s="1">
+      <c r="E24" s="15">
         <v>26</v>
       </c>
-      <c r="F24" s="7" t="s">
+      <c r="F24" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="G24" s="7" t="s">
+      <c r="G24" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H24" s="1">
+      <c r="H24" s="15">
         <v>89</v>
       </c>
-      <c r="I24" s="1">
+      <c r="I24" s="15">
         <v>120</v>
       </c>
-      <c r="J24" s="1">
+      <c r="J24" s="15">
         <v>25712</v>
       </c>
     </row>
     <row r="25" spans="1:10">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="B25" s="1">
+      <c r="B25" s="15">
         <v>7600</v>
       </c>
-      <c r="C25" s="1">
+      <c r="C25" s="15">
         <v>510</v>
       </c>
-      <c r="D25" s="1">
+      <c r="D25" s="15">
         <v>107</v>
       </c>
-      <c r="E25" s="1">
-        <v>0</v>
-      </c>
-      <c r="F25" s="7" t="s">
+      <c r="E25" s="15">
+        <v>0</v>
+      </c>
+      <c r="F25" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="G25" s="7" t="s">
+      <c r="G25" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H25" s="1">
+      <c r="H25" s="15">
         <v>15</v>
       </c>
-      <c r="I25" s="1">
+      <c r="I25" s="15">
         <v>44</v>
       </c>
-      <c r="J25" s="1">
+      <c r="J25" s="15">
         <v>8286</v>
       </c>
     </row>
     <row r="26" spans="1:10">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B26" s="1">
+      <c r="B26" s="15">
         <v>1508</v>
       </c>
-      <c r="C26" s="1">
+      <c r="C26" s="15">
         <v>82</v>
       </c>
-      <c r="D26" s="1">
+      <c r="D26" s="15">
         <v>79</v>
       </c>
-      <c r="E26" s="1">
+      <c r="E26" s="15">
         <v>3</v>
       </c>
-      <c r="F26" s="1">
-        <v>0</v>
-      </c>
-      <c r="G26" s="1">
-        <v>0</v>
-      </c>
-      <c r="H26" s="1">
-        <v>0</v>
-      </c>
-      <c r="I26" s="1">
+      <c r="F26" s="15">
+        <v>0</v>
+      </c>
+      <c r="G26" s="15">
+        <v>0</v>
+      </c>
+      <c r="H26" s="15">
+        <v>0</v>
+      </c>
+      <c r="I26" s="15">
         <v>5</v>
       </c>
-      <c r="J26" s="1">
+      <c r="J26" s="15">
         <v>1677</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="13">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="B27" s="3">
+      <c r="B27" s="18">
         <v>439549</v>
       </c>
-      <c r="C27" s="3">
+      <c r="C27" s="18">
         <v>28054</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="18">
         <v>3226</v>
       </c>
-      <c r="E27" s="3">
+      <c r="E27" s="18">
         <v>217</v>
       </c>
-      <c r="F27" s="3">
+      <c r="F27" s="18">
         <v>77</v>
       </c>
-      <c r="G27" s="3">
+      <c r="G27" s="18">
         <v>1164</v>
       </c>
-      <c r="H27" s="3">
+      <c r="H27" s="18">
         <v>602</v>
       </c>
-      <c r="I27" s="3">
+      <c r="I27" s="18">
         <v>4062</v>
       </c>
-      <c r="J27" s="3">
+      <c r="J27" s="18">
         <v>476951</v>
       </c>
     </row>
     <row r="28" spans="1:10">
-      <c r="A28" s="20"/>
-      <c r="B28" s="19"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="19"/>
-      <c r="I28" s="19"/>
-      <c r="J28" s="19"/>
+      <c r="A28" s="16"/>
+      <c r="B28" s="15"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="15"/>
+      <c r="H28" s="15"/>
+      <c r="I28" s="15"/>
+      <c r="J28" s="15"/>
     </row>
     <row r="29" spans="1:10" ht="13">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B29" s="19"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="19"/>
-      <c r="H29" s="19"/>
-      <c r="I29" s="19"/>
-      <c r="J29" s="19"/>
+      <c r="B29" s="15"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="15"/>
+      <c r="H29" s="15"/>
+      <c r="I29" s="15"/>
+      <c r="J29" s="15"/>
     </row>
     <row r="30" spans="1:10">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B30" s="1">
+      <c r="B30" s="15">
         <v>119814</v>
       </c>
-      <c r="C30" s="1">
+      <c r="C30" s="15">
         <v>3054</v>
       </c>
-      <c r="D30" s="1">
+      <c r="D30" s="15">
         <v>961</v>
       </c>
-      <c r="E30" s="1">
+      <c r="E30" s="15">
         <v>18</v>
       </c>
-      <c r="F30" s="1">
+      <c r="F30" s="15">
         <v>8</v>
       </c>
-      <c r="G30" s="1">
+      <c r="G30" s="15">
         <v>47</v>
       </c>
-      <c r="H30" s="1">
+      <c r="H30" s="15">
         <v>69</v>
       </c>
-      <c r="I30" s="1">
+      <c r="I30" s="15">
         <v>556</v>
       </c>
-      <c r="J30" s="1">
+      <c r="J30" s="15">
         <v>124527</v>
       </c>
     </row>
     <row r="31" spans="1:10">
-      <c r="A31" s="5" t="s">
+      <c r="A31" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="B31" s="1">
+      <c r="B31" s="15">
         <v>9492</v>
       </c>
-      <c r="C31" s="1">
+      <c r="C31" s="15">
         <v>179</v>
       </c>
-      <c r="D31" s="1">
+      <c r="D31" s="15">
         <v>24</v>
       </c>
-      <c r="E31" s="1">
+      <c r="E31" s="15">
         <v>8</v>
       </c>
-      <c r="F31" s="1">
+      <c r="F31" s="15">
         <v>4</v>
       </c>
-      <c r="G31" s="7" t="s">
+      <c r="G31" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H31" s="1">
+      <c r="H31" s="15">
         <v>38</v>
       </c>
-      <c r="I31" s="7" t="s">
+      <c r="I31" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="J31" s="4">
+      <c r="J31" s="19">
         <v>9792</v>
       </c>
     </row>
     <row r="32" spans="1:10">
-      <c r="A32" s="5" t="s">
+      <c r="A32" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="B32" s="1">
+      <c r="B32" s="15">
         <v>283</v>
       </c>
-      <c r="C32" s="1">
+      <c r="C32" s="15">
         <v>49</v>
       </c>
-      <c r="D32" s="1">
+      <c r="D32" s="15">
         <v>109</v>
       </c>
-      <c r="E32" s="1">
-        <v>0</v>
-      </c>
-      <c r="F32" s="1">
-        <v>0</v>
-      </c>
-      <c r="G32" s="7" t="s">
+      <c r="E32" s="15">
+        <v>0</v>
+      </c>
+      <c r="F32" s="15">
+        <v>0</v>
+      </c>
+      <c r="G32" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H32" s="1">
+      <c r="H32" s="15">
         <v>8</v>
       </c>
-      <c r="I32" s="7" t="s">
+      <c r="I32" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="J32" s="4">
+      <c r="J32" s="19">
         <v>454</v>
       </c>
     </row>
@@ -1341,25 +1336,25 @@
       <c r="A35" s="5"/>
     </row>
     <row r="36" spans="1:10" ht="13" thickBot="1">
-      <c r="A36" s="8"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="8"/>
-      <c r="H36" s="8"/>
-      <c r="I36" s="8"/>
-      <c r="J36" s="8"/>
+      <c r="A36" s="7"/>
+      <c r="B36" s="7"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="7"/>
+      <c r="H36" s="7"/>
+      <c r="I36" s="7"/>
+      <c r="J36" s="7"/>
     </row>
     <row r="37" spans="1:10" ht="13" thickTop="1"/>
     <row r="39" spans="1:10">
-      <c r="A39" s="11" t="s">
+      <c r="A39" s="10" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="41" spans="1:10">
-      <c r="B41" s="9"/>
+      <c r="B41" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
